--- a/data/UserManger/create_user.xlsx
+++ b/data/UserManger/create_user.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9300" activeTab="1"/>
+    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>allureEpic</t>
   </si>
@@ -71,9 +71,6 @@
     <t>assert</t>
   </si>
   <si>
-    <t>sql</t>
-  </si>
-  <si>
     <t>create_user_01</t>
   </si>
   <si>
@@ -89,7 +86,8 @@
     <t>创建用户成功（必填参数）</t>
   </si>
   <si>
-    <t>{'Content-Type': 'application/json', 'Authorization': '$cache{token}'}</t>
+    <t>{'Content-Type': 'application/json', 
+'Authorization': '$cache{token}'}</t>
   </si>
   <si>
     <t>json</t>
@@ -1080,11 +1078,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8796296296296" customWidth="1"/>
-    <col min="2" max="2" width="15.6296296296296" customWidth="1"/>
-    <col min="3" max="3" width="18.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="22.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1121,17 +1119,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="16.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.6296296296296" customWidth="1"/>
+    <col min="4" max="4" width="10.6333333333333" customWidth="1"/>
     <col min="5" max="5" width="25.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="12.3796296296296" customWidth="1"/>
-    <col min="8" max="8" width="12.6296296296296" customWidth="1"/>
-    <col min="9" max="9" width="5.62962962962963" customWidth="1"/>
+    <col min="7" max="7" width="12.3833333333333" customWidth="1"/>
+    <col min="8" max="8" width="12.6333333333333" customWidth="1"/>
+    <col min="9" max="9" width="9.125" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="7.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
@@ -1174,43 +1172,41 @@
       <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="M1" s="1"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" ht="41" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M2" s="4"/>
     </row>
@@ -1349,7 +1345,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:15">
+    <row r="12" ht="18" customHeight="1" spans="1:13">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1363,8 +1359,6 @@
       <c r="K12" s="2"/>
       <c r="L12" s="3"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:13">
       <c r="A13" s="4"/>

--- a/data/UserManger/create_user.xlsx
+++ b/data/UserManger/create_user.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>allureEpic</t>
   </si>
@@ -93,7 +93,10 @@
     <t>json</t>
   </si>
   <si>
-    <t>{'username': 'NTU44ug521', 'password': 'W^20XxT1'}</t>
+    <t>{'username': '${{get_username()}}', 'password': '${{get_password()}}'}</t>
+  </si>
+  <si>
+    <t>flase</t>
   </si>
   <si>
     <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 201, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '创建成功', 'AssertType': None}}</t>
@@ -1078,11 +1081,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8833333333333" customWidth="1"/>
-    <col min="2" max="2" width="15.6333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
+    <col min="1" max="1" width="22.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="15.6296296296296" customWidth="1"/>
+    <col min="3" max="3" width="18.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1119,18 +1122,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.6333333333333" customWidth="1"/>
-    <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="16.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.6333333333333" customWidth="1"/>
+    <col min="4" max="4" width="10.6296296296296" customWidth="1"/>
     <col min="5" max="5" width="25.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="12.3833333333333" customWidth="1"/>
-    <col min="8" max="8" width="12.6333333333333" customWidth="1"/>
-    <col min="9" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="7" max="7" width="12.3796296296296" customWidth="1"/>
+    <col min="8" max="8" width="12.6296296296296" customWidth="1"/>
+    <col min="9" max="9" width="9.12962962962963" customWidth="1"/>
+    <col min="10" max="10" width="21.6666666666667" customWidth="1"/>
     <col min="11" max="11" width="7.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
   </cols>
@@ -1203,10 +1206,12 @@
       <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="3"/>
+      <c r="J2" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="4"/>
     </row>

--- a/data/UserManger/create_user.xlsx
+++ b/data/UserManger/create_user.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9300" activeTab="1"/>
+    <workbookView windowWidth="15960" windowHeight="9870" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="77">
   <si>
     <t>allureEpic</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>assert</t>
+  </si>
+  <si>
+    <t>teardown</t>
   </si>
   <si>
     <t>create_user_01</t>
@@ -93,13 +96,175 @@
     <t>json</t>
   </si>
   <si>
-    <t>{'username': '${{get_username()}}', 'password': '${{get_password()}}'}</t>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_password()}}'}</t>
   </si>
   <si>
     <t>flase</t>
   </si>
   <si>
     <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 201, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '创建成功', 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>[{'case_id': 'delete_user_01', 'send_request': [{'dependent_type': 'response', 'jsonpath': '$.data.id', 'replace_key': '$.data.id'}]}]</t>
+  </si>
+  <si>
+    <t>create_user_02</t>
+  </si>
+  <si>
+    <t>创建用户成功（必填+选填参数）</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_password()}}!',
+'email': '${{get_email()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_03</t>
+  </si>
+  <si>
+    <t>创建用户成功（全部参数）</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_password()}}!',
+'email': '${{get_email()}}',
+'mobile': "${{get_phone()}}"}</t>
+  </si>
+  <si>
+    <t>create_user_04</t>
+  </si>
+  <si>
+    <t>创建已存在用户</t>
+  </si>
+  <si>
+    <t>{'username': 'admin',
+'password': '123456'}</t>
+  </si>
+  <si>
+    <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 400, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '用户名已存在', 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>create_user_05</t>
+  </si>
+  <si>
+    <t>用户名为空</t>
+  </si>
+  <si>
+    <t>{'username': '',
+'password': '123456'}</t>
+  </si>
+  <si>
+    <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 400, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '用户名不能为空', 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>create_user_06</t>
+  </si>
+  <si>
+    <t>用户名纯数字</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_number()}}',
+'password': '123456'}</t>
+  </si>
+  <si>
+    <t>create_user_07</t>
+  </si>
+  <si>
+    <t>用户名纯字母</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_char()}}',
+'password': '123456'}</t>
+  </si>
+  <si>
+    <t>create_user_08</t>
+  </si>
+  <si>
+    <t>用户名包含中文、特殊字符</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_name()}}${{get_char()}}',
+'password': '123456'}</t>
+  </si>
+  <si>
+    <t>create_user_09</t>
+  </si>
+  <si>
+    <t>密码为空</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': ''}</t>
+  </si>
+  <si>
+    <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 400, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '密码不能为空', 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>create_user_10</t>
+  </si>
+  <si>
+    <t>密码为纯数字</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_number()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_11</t>
+  </si>
+  <si>
+    <t>密码为纯字母</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_char()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_12</t>
+  </si>
+  <si>
+    <t>100位密码</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '{{custom_param()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_13</t>
+  </si>
+  <si>
+    <t>多参：多abc</t>
+  </si>
+  <si>
+    <t>{'username': '${{get_username()}}',
+'password': '${{get_password()}}',
+'abc': '${{get_number()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_14</t>
+  </si>
+  <si>
+    <t>少参：缺少username</t>
+  </si>
+  <si>
+    <t>{'password': '${{get_password()}}'}</t>
+  </si>
+  <si>
+    <t>create_user_15</t>
+  </si>
+  <si>
+    <t>没有参数</t>
+  </si>
+  <si>
+    <t>create_user_16</t>
+  </si>
+  <si>
+    <t>错误参数：修改username为test</t>
+  </si>
+  <si>
+    <t>{'test': '${{get_username()}}',
+'password': '${{get_password()}}'}</t>
   </si>
 </sst>
 </file>
@@ -1081,11 +1246,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8796296296296" customWidth="1"/>
-    <col min="2" max="2" width="15.6296296296296" customWidth="1"/>
-    <col min="3" max="3" width="18.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="22.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1122,17 +1287,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="16.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="16.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="10.6296296296296" customWidth="1"/>
+    <col min="4" max="4" width="10.6333333333333" customWidth="1"/>
     <col min="5" max="5" width="25.5" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="12.3796296296296" customWidth="1"/>
-    <col min="8" max="8" width="12.6296296296296" customWidth="1"/>
-    <col min="9" max="9" width="9.12962962962963" customWidth="1"/>
+    <col min="7" max="7" width="12.3833333333333" customWidth="1"/>
+    <col min="8" max="8" width="12.6333333333333" customWidth="1"/>
+    <col min="9" max="9" width="9.13333333333333" customWidth="1"/>
     <col min="10" max="10" width="21.6666666666667" customWidth="1"/>
     <col min="11" max="11" width="7.25" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
@@ -1175,269 +1340,575 @@
       <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
     </row>
     <row r="2" ht="41" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" ht="51" customHeight="1" spans="1:13">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" ht="51" customHeight="1" spans="1:13">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="4"/>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" ht="51" customHeight="1" spans="1:13">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="4"/>
+      <c r="L4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="4"/>
+      <c r="I5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="4"/>
+      <c r="I6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="4"/>
+      <c r="I7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="4"/>
+      <c r="I8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="4"/>
+      <c r="I9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="4"/>
+      <c r="I10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="A11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="4"/>
+      <c r="I11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:13">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="4"/>
+      <c r="L12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="4"/>
+      <c r="I13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:13">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="4"/>
+      <c r="I14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="I15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:13">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="A16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="L16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="2"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:13">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="A17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="6"/>
+      <c r="I17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="L17" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13">
@@ -1452,7 +1923,7 @@
       <c r="I18" s="4"/>
       <c r="J18" s="6"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="4"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13">
@@ -1467,7 +1938,7 @@
       <c r="I19" s="4"/>
       <c r="J19" s="6"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="L19" s="2"/>
       <c r="M19" s="4"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13">
